--- a/sample/注文書.xlsx
+++ b/sample/注文書.xlsx
@@ -285,8 +285,94 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><numFmts count="2"><numFmt numFmtId="164" formatCode="#,##0"/><numFmt numFmtId="165" formatCode="¥#,##0"/></numFmts><fonts count="3"><font></font><font><sz val="18"/><b/></font><font><b/></font></fonts><fills count="4"><fill><patternFill patternType="none"/></fill><fill><patternFill patternType="gray125"/></fill><fill><patternFill patternType="solid"><fgColor rgb="FFF2F2F2"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor rgb="FFDCE6F1"/><bgColor indexed="64"/></patternFill></fill></fills><borders count="2"><border><left/><right/><top/><bottom/><diagonal/></border><border><left style="thin"><color indexed="64"/></left><right style="thin"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border></borders><cellStyleXfs count="1"><xf numFmtId="0" fontId="0" fillId="0" borderId="0"/></cellStyleXfs><cellXfs count="11"><xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/><xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/></xf><xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/><xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/><xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/><xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/></xf><xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/><xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/></xf><xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/><xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/></xf><xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0"applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/></cellXfs><cellStyles count="1"><cellStyle name="標準" xfId="0" builtinId="0"/></cellStyles></styleSheet>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="¥#,##0"/>
+  </numFmts>
+  <fonts count="3">
+    <font/>
+    <font>
+      <sz val="18"/>
+      <b/>
+    </font>
+    <font>
+      <b/>
+    </font>
+  </fonts>
+  <fills count="4">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
